--- a/backend/data/hpt_records.xlsx
+++ b/backend/data/hpt_records.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>County Allocation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>525000</v>
+        <v>562500</v>
       </c>
       <c r="F2" t="n">
-        <v>472500</v>
+        <v>506250</v>
       </c>
       <c r="G2" t="n">
-        <v>31500</v>
+        <v>28125</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -514,29 +514,29 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18137</v>
+        <v>14190</v>
       </c>
       <c r="B3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="F3" t="n">
-        <v>360000</v>
+        <v>90000</v>
       </c>
       <c r="G3" t="n">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -551,29 +551,29 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32058</v>
+        <v>28410</v>
       </c>
       <c r="B4" t="n">
-        <v>1250000</v>
+        <v>750000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>Partner Funding</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>562500</v>
+        <v>300000</v>
       </c>
       <c r="F4" t="n">
-        <v>253125</v>
+        <v>225000</v>
       </c>
       <c r="G4" t="n">
-        <v>28125</v>
+        <v>18000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -588,64 +588,66 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14183</v>
+        <v>21455</v>
       </c>
       <c r="B5" t="n">
-        <v>500000</v>
+        <v>2500000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>County Allocation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1012500</v>
+      </c>
+      <c r="G5" t="n">
+        <v>67500</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sample_document.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>demo_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>18439</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Partner Funding</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12500</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>sample_document.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>demo_user</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Partner Funding</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>840000</v>
+        <v>450000</v>
       </c>
       <c r="F6" t="n">
-        <v>504000</v>
+        <v>202500</v>
       </c>
       <c r="G6" t="n">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +662,19 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18372</v>
+        <v>19885</v>
       </c>
       <c r="B7" t="n">
         <v>500000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Partner Funding</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -682,7 +684,7 @@
         <v>135000</v>
       </c>
       <c r="G7" t="n">
-        <v>11250</v>
+        <v>18000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,29 +699,29 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24675</v>
+        <v>18009</v>
       </c>
       <c r="B8" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>840000</v>
+        <v>750000</v>
       </c>
       <c r="F8" t="n">
-        <v>630000</v>
+        <v>562500</v>
       </c>
       <c r="G8" t="n">
-        <v>50400</v>
+        <v>75000</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,29 +736,29 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32607</v>
+        <v>14207</v>
       </c>
       <c r="B9" t="n">
-        <v>750000</v>
+        <v>1250000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Partner Funding</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>300000</v>
+        <v>562500</v>
       </c>
       <c r="F9" t="n">
-        <v>225000</v>
+        <v>337500</v>
       </c>
       <c r="G9" t="n">
-        <v>15000</v>
+        <v>33750</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,29 +773,29 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18382</v>
+        <v>14213</v>
       </c>
       <c r="B10" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>County Allocation</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225000</v>
+        <v>800000</v>
       </c>
       <c r="F10" t="n">
-        <v>135000</v>
+        <v>480000</v>
       </c>
       <c r="G10" t="n">
-        <v>22500</v>
+        <v>80000</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,10 +810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>23455</v>
+        <v>15762</v>
       </c>
       <c r="B11" t="n">
-        <v>750000</v>
+        <v>2500000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -820,17 +822,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>375000</v>
+        <v>1050000</v>
       </c>
       <c r="F11" t="n">
-        <v>337500</v>
+        <v>630000</v>
       </c>
       <c r="G11" t="n">
-        <v>22500</v>
+        <v>84000</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,10 +847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23130</v>
+        <v>14222</v>
       </c>
       <c r="B12" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -857,17 +859,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="F12" t="n">
-        <v>180000</v>
+        <v>168750</v>
       </c>
       <c r="G12" t="n">
-        <v>9000</v>
+        <v>6750</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,29 +884,29 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20265</v>
+        <v>14223</v>
       </c>
       <c r="B13" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>Partner Funding</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210000</v>
+        <v>900000</v>
       </c>
       <c r="F13" t="n">
-        <v>157500</v>
+        <v>675000</v>
       </c>
       <c r="G13" t="n">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,29 +921,29 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18440</v>
+        <v>14224</v>
       </c>
       <c r="B14" t="n">
         <v>2500000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Partner Funding</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>875000</v>
+        <v>625000</v>
       </c>
       <c r="F14" t="n">
-        <v>656250</v>
+        <v>375000</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,7 +958,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22937</v>
+        <v>14226</v>
       </c>
       <c r="B15" t="n">
         <v>500000</v>
@@ -968,17 +970,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F15" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="G15" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,29 +995,29 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14188</v>
+        <v>17302</v>
       </c>
       <c r="B16" t="n">
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>200000</v>
+        <v>750000</v>
       </c>
       <c r="F16" t="n">
-        <v>180000</v>
+        <v>562500</v>
       </c>
       <c r="G16" t="n">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,29 +1032,29 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31271</v>
+        <v>17793</v>
       </c>
       <c r="B17" t="n">
-        <v>2000000</v>
+        <v>1250000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>500000</v>
+        <v>437500</v>
       </c>
       <c r="F17" t="n">
-        <v>300000</v>
+        <v>328125</v>
       </c>
       <c r="G17" t="n">
-        <v>10000</v>
+        <v>17500</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,10 +1069,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32090</v>
+        <v>23444</v>
       </c>
       <c r="B18" t="n">
-        <v>500000</v>
+        <v>2500000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1079,17 +1081,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50000</v>
+        <v>875000</v>
       </c>
       <c r="F18" t="n">
-        <v>37500</v>
+        <v>525000</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>26250</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,29 +1106,29 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19335</v>
+        <v>14251</v>
       </c>
       <c r="B19" t="n">
-        <v>1500000</v>
+        <v>1250000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>450000</v>
+        <v>437500</v>
       </c>
       <c r="F19" t="n">
-        <v>337500</v>
+        <v>196875</v>
       </c>
       <c r="G19" t="n">
-        <v>18000</v>
+        <v>4375</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1140,11 +1142,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>20226</v>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>2000000</v>
+        <v>1250000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>400000</v>
+        <v>187500</v>
       </c>
       <c r="F20" t="n">
-        <v>360000</v>
+        <v>140625</v>
       </c>
       <c r="G20" t="n">
-        <v>12000</v>
+        <v>1875</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1177,30 +1177,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>29215</v>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1500000</v>
+        <v>750000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Partner Funding</t>
+          <t>County Allocation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>300000</v>
+        <v>187500</v>
       </c>
       <c r="F21" t="n">
-        <v>270000</v>
+        <v>168750</v>
       </c>
       <c r="G21" t="n">
-        <v>3000</v>
+        <v>1875</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1215,10 +1213,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14190</v>
+        <v>14263</v>
       </c>
       <c r="B22" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1227,17 +1225,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="F22" t="n">
-        <v>90000</v>
+        <v>270000</v>
       </c>
       <c r="G22" t="n">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1252,29 +1250,29 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>27426</v>
+        <v>14265</v>
       </c>
       <c r="B23" t="n">
         <v>750000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>Partner Funding</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>225000</v>
+        <v>112500</v>
       </c>
       <c r="F23" t="n">
-        <v>202500</v>
+        <v>67500</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1289,10 +1287,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14191</v>
+        <v>32556</v>
       </c>
       <c r="B24" t="n">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1301,17 +1299,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>350000</v>
+        <v>300000</v>
       </c>
       <c r="F24" t="n">
-        <v>157500</v>
+        <v>225000</v>
       </c>
       <c r="G24" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1326,29 +1324,29 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>28410</v>
+        <v>14279</v>
       </c>
       <c r="B25" t="n">
-        <v>1250000</v>
+        <v>1500000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FIF</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>250000</v>
+        <v>375000</v>
       </c>
       <c r="F25" t="n">
-        <v>112500</v>
+        <v>281250</v>
       </c>
       <c r="G25" t="n">
-        <v>5000</v>
+        <v>3750</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1363,10 +1361,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21455</v>
+        <v>18378</v>
       </c>
       <c r="B26" t="n">
-        <v>1250000</v>
+        <v>1000000</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1379,13 +1377,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>250000</v>
+        <v>100000</v>
       </c>
       <c r="F26" t="n">
-        <v>112500</v>
+        <v>75000</v>
       </c>
       <c r="G26" t="n">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1400,29 +1398,29 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18439</v>
+        <v>14291</v>
       </c>
       <c r="B27" t="n">
-        <v>2500000</v>
+        <v>1500000</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="F27" t="n">
-        <v>375000</v>
+        <v>337500</v>
       </c>
       <c r="G27" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1437,29 +1435,29 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>19885</v>
+        <v>14312</v>
       </c>
       <c r="B28" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Partner Funding</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="F28" t="n">
-        <v>187500</v>
+        <v>225000</v>
       </c>
       <c r="G28" t="n">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1474,29 +1472,29 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22886</v>
+        <v>14328</v>
       </c>
       <c r="B29" t="n">
-        <v>1250000</v>
+        <v>1000000</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>County Allocation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>125000</v>
+        <v>350000</v>
       </c>
       <c r="F29" t="n">
-        <v>56250</v>
+        <v>157500</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1511,29 +1509,29 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>18009</v>
+        <v>21601</v>
       </c>
       <c r="B30" t="n">
-        <v>500000</v>
+        <v>1250000</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150000</v>
+        <v>250000</v>
       </c>
       <c r="F30" t="n">
-        <v>135000</v>
+        <v>225000</v>
       </c>
       <c r="G30" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1548,29 +1546,29 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23821</v>
+        <v>14357</v>
       </c>
       <c r="B31" t="n">
-        <v>1500000</v>
+        <v>750000</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>County Allocation</t>
+          <t>FIF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="F31" t="n">
-        <v>270000</v>
+        <v>101250</v>
       </c>
       <c r="G31" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>

--- a/backend/data/hpt_records.xlsx
+++ b/backend/data/hpt_records.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -55,9 +58,6 @@
   </si>
   <si>
     <t>submission_date</t>
-  </si>
-  <si>
-    <t>Facility Collection (Out of Pocket)</t>
   </si>
   <si>
     <t>SHIF</t>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>2026-06-03 12:45:04</t>
+  </si>
+  <si>
+    <t>PHC</t>
   </si>
 </sst>
 </file>
@@ -535,6 +538,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="23.90625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -582,10 +588,10 @@
         <v>1232100</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2">
         <v>621607.46</v>
@@ -597,16 +603,16 @@
         <v>23667.97</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -617,10 +623,10 @@
         <v>1364400</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>219404.56</v>
@@ -632,16 +638,16 @@
         <v>19417.37</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -652,10 +658,10 @@
         <v>1262100</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>685315.99</v>
@@ -667,16 +673,16 @@
         <v>10523.12</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -687,10 +693,10 @@
         <v>1029700</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>595260.81999999995</v>
@@ -702,16 +708,16 @@
         <v>18413.66</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -722,10 +728,10 @@
         <v>1014000</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
       </c>
       <c r="E6">
         <v>600246.65</v>
@@ -737,16 +743,16 @@
         <v>35552.58</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -757,10 +763,10 @@
         <v>599700</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>265355.58</v>
@@ -772,16 +778,16 @@
         <v>20047.5</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -792,10 +798,10 @@
         <v>404500</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>189860.32</v>
@@ -807,16 +813,16 @@
         <v>14942.89</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -827,10 +833,10 @@
         <v>449400</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>219019.86</v>
@@ -842,16 +848,16 @@
         <v>6036.56</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -862,10 +868,10 @@
         <v>456900</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>158560.81</v>
@@ -877,16 +883,16 @@
         <v>10060.790000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -897,10 +903,10 @@
         <v>582500</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>347438.49</v>
@@ -912,16 +918,16 @@
         <v>21508.01</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" t="s">
         <v>44</v>
-      </c>
-      <c r="K11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -932,10 +938,10 @@
         <v>805400</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12">
         <v>483226.17</v>
@@ -947,16 +953,16 @@
         <v>6707.67</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -967,10 +973,10 @@
         <v>885100</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13">
         <v>302358.7</v>
@@ -982,16 +988,16 @@
         <v>7843.26</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -1002,10 +1008,10 @@
         <v>624300</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14">
         <v>120653.52</v>
@@ -1017,16 +1023,16 @@
         <v>1758.44</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -1037,10 +1043,10 @@
         <v>675500</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>168104.27</v>
@@ -1052,16 +1058,16 @@
         <v>9397.9</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -1072,10 +1078,10 @@
         <v>712700</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>379215.1</v>
@@ -1087,16 +1093,16 @@
         <v>29942.26</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K16" t="s">
         <v>44</v>
-      </c>
-      <c r="K16" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -1107,10 +1113,10 @@
         <v>2165900</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>778304.25</v>
@@ -1122,16 +1128,16 @@
         <v>6459.43</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -1142,10 +1148,10 @@
         <v>2226700</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>1250334.82</v>
@@ -1157,16 +1163,16 @@
         <v>103115.05</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -1177,10 +1183,10 @@
         <v>2517500</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>539328.24</v>
@@ -1192,16 +1198,16 @@
         <v>5562.1</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -1212,10 +1218,10 @@
         <v>2546100</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20">
         <v>696571.35</v>
@@ -1227,16 +1233,16 @@
         <v>57895.93</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -1247,10 +1253,10 @@
         <v>2672700</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21">
         <v>1230363.6399999999</v>
@@ -1262,16 +1268,16 @@
         <v>11198.92</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -1282,10 +1288,10 @@
         <v>1064400</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22">
         <v>486950</v>
@@ -1297,16 +1303,16 @@
         <v>32264.65</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -1317,10 +1323,10 @@
         <v>887200</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23">
         <v>237897.44</v>
@@ -1332,16 +1338,16 @@
         <v>13608.58</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
@@ -1352,10 +1358,10 @@
         <v>963700</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24">
         <v>240681.65</v>
@@ -1367,16 +1373,16 @@
         <v>12577.8</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
@@ -1387,10 +1393,10 @@
         <v>981000</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25">
         <v>462820.34</v>
@@ -1402,16 +1408,16 @@
         <v>26797.1</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
@@ -1422,10 +1428,10 @@
         <v>924000</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26">
         <v>235944.78</v>
@@ -1437,16 +1443,16 @@
         <v>13124</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
@@ -1457,10 +1463,10 @@
         <v>489100</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27">
         <v>275340.65000000002</v>
@@ -1472,16 +1478,16 @@
         <v>13934.44</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
@@ -1492,10 +1498,10 @@
         <v>587800</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28">
         <v>260925.12</v>
@@ -1507,16 +1513,16 @@
         <v>15565.42</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
@@ -1527,10 +1533,10 @@
         <v>594600</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <v>325984.03000000003</v>
@@ -1542,16 +1548,16 @@
         <v>26740.87</v>
       </c>
       <c r="H29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
@@ -1562,10 +1568,10 @@
         <v>402300</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30">
         <v>241014.15</v>
@@ -1577,16 +1583,16 @@
         <v>3531.77</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
@@ -1597,10 +1603,10 @@
         <v>506600</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31">
         <v>293659.14</v>
@@ -1612,16 +1618,16 @@
         <v>25223.58</v>
       </c>
       <c r="H31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
@@ -1632,10 +1638,10 @@
         <v>1606900</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32">
         <v>285022.14</v>
@@ -1647,16 +1653,16 @@
         <v>23453.7</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
@@ -1667,10 +1673,10 @@
         <v>1510400</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E33">
         <v>678534.28</v>
@@ -1682,16 +1688,16 @@
         <v>36640.019999999997</v>
       </c>
       <c r="H33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
@@ -1702,10 +1708,10 @@
         <v>1474400</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34">
         <v>643645.36</v>
@@ -1717,16 +1723,16 @@
         <v>54294.87</v>
       </c>
       <c r="H34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -1737,10 +1743,10 @@
         <v>1802300</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E35">
         <v>420108.97</v>
@@ -1752,16 +1758,16 @@
         <v>22942.28</v>
       </c>
       <c r="H35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
@@ -1772,10 +1778,10 @@
         <v>1452400</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36">
         <v>588377.86</v>
@@ -1787,16 +1793,16 @@
         <v>10195.51</v>
       </c>
       <c r="H36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
@@ -1807,10 +1813,10 @@
         <v>1312400</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E37">
         <v>717548.53</v>
@@ -1822,16 +1828,16 @@
         <v>57992.78</v>
       </c>
       <c r="H37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
@@ -1842,10 +1848,10 @@
         <v>1554900</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E38">
         <v>865918.58</v>
@@ -1857,16 +1863,16 @@
         <v>69452.399999999994</v>
       </c>
       <c r="H38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
@@ -1877,10 +1883,10 @@
         <v>1003300</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E39">
         <v>446528.91</v>
@@ -1892,16 +1898,16 @@
         <v>14091.94</v>
       </c>
       <c r="H39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
@@ -1912,10 +1918,10 @@
         <v>1130900</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E40">
         <v>457658.5</v>
@@ -1927,16 +1933,16 @@
         <v>21814.97</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
@@ -1947,10 +1953,10 @@
         <v>1178600</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41">
         <v>669302.53</v>
@@ -1962,16 +1968,16 @@
         <v>49932.59</v>
       </c>
       <c r="H41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
@@ -1982,10 +1988,10 @@
         <v>2314300</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E42">
         <v>477423.61</v>
@@ -1997,16 +2003,16 @@
         <v>42324.59</v>
       </c>
       <c r="H42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
@@ -2017,10 +2023,10 @@
         <v>1814800</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43">
         <v>956956.55</v>
@@ -2032,16 +2038,16 @@
         <v>81699.66</v>
       </c>
       <c r="H43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
@@ -2052,10 +2058,10 @@
         <v>2204600</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E44">
         <v>619155.68999999994</v>
@@ -2067,16 +2073,16 @@
         <v>37641.71</v>
       </c>
       <c r="H44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
@@ -2087,10 +2093,10 @@
         <v>1874300</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45">
         <v>957878.74</v>
@@ -2102,16 +2108,16 @@
         <v>14251.32</v>
       </c>
       <c r="H45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
@@ -2122,10 +2128,10 @@
         <v>1625800</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46">
         <v>901121.42</v>
@@ -2137,16 +2143,16 @@
         <v>69369.960000000006</v>
       </c>
       <c r="H46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J46" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
@@ -2157,10 +2163,10 @@
         <v>2804100</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E47">
         <v>1231574.76</v>
@@ -2172,16 +2178,16 @@
         <v>82554.45</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
@@ -2192,10 +2198,10 @@
         <v>3064400</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48">
         <v>1330466.78</v>
@@ -2207,16 +2213,16 @@
         <v>91364.41</v>
       </c>
       <c r="H48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
@@ -2227,10 +2233,10 @@
         <v>2851400</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49">
         <v>485161.42</v>
@@ -2242,16 +2248,16 @@
         <v>32846.22</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
@@ -2262,10 +2268,10 @@
         <v>2395100</v>
       </c>
       <c r="C50" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E50">
         <v>1195899.25</v>
@@ -2277,16 +2283,16 @@
         <v>2695.99</v>
       </c>
       <c r="H50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
@@ -2297,10 +2303,10 @@
         <v>2551200</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E51">
         <v>857088.78</v>
@@ -2312,16 +2318,16 @@
         <v>44173.25</v>
       </c>
       <c r="H51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J51" t="s">
+        <v>43</v>
+      </c>
+      <c r="K51" t="s">
         <v>44</v>
-      </c>
-      <c r="K51" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
@@ -2332,10 +2338,10 @@
         <v>549400</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E52">
         <v>100691.9</v>
@@ -2347,16 +2353,16 @@
         <v>4688.84</v>
       </c>
       <c r="H52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
@@ -2367,10 +2373,10 @@
         <v>622900</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E53">
         <v>216868.39</v>
@@ -2382,16 +2388,16 @@
         <v>13096.14</v>
       </c>
       <c r="H53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
@@ -2402,10 +2408,10 @@
         <v>619000</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54">
         <v>172561.21</v>
@@ -2417,16 +2423,16 @@
         <v>11492.64</v>
       </c>
       <c r="H54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
@@ -2437,10 +2443,10 @@
         <v>481600</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55">
         <v>137527.12</v>
@@ -2452,16 +2458,16 @@
         <v>8058.74</v>
       </c>
       <c r="H55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
@@ -2472,10 +2478,10 @@
         <v>465500</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56">
         <v>261459.08</v>
@@ -2487,16 +2493,16 @@
         <v>13693.78</v>
       </c>
       <c r="H56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
@@ -2507,10 +2513,10 @@
         <v>1836900</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57">
         <v>926064.18</v>
@@ -2522,16 +2528,16 @@
         <v>49908.959999999999</v>
       </c>
       <c r="H57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
@@ -2542,10 +2548,10 @@
         <v>2089000</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58">
         <v>1184030.02</v>
@@ -2557,16 +2563,16 @@
         <v>59257.81</v>
       </c>
       <c r="H58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
@@ -2577,10 +2583,10 @@
         <v>2249200</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E59">
         <v>1306102.1399999999</v>
@@ -2592,16 +2598,16 @@
         <v>11983.49</v>
       </c>
       <c r="H59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
@@ -2612,10 +2618,10 @@
         <v>1940000</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E60">
         <v>711414.84</v>
@@ -2627,16 +2633,16 @@
         <v>43602.02</v>
       </c>
       <c r="H60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
@@ -2647,10 +2653,10 @@
         <v>2222800</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61">
         <v>469239.59</v>
@@ -2662,16 +2668,16 @@
         <v>37612.050000000003</v>
       </c>
       <c r="H61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
@@ -2682,10 +2688,10 @@
         <v>2433000</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E62">
         <v>1210602.3600000001</v>
@@ -2697,16 +2703,16 @@
         <v>91617.99</v>
       </c>
       <c r="H62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
@@ -2717,10 +2723,10 @@
         <v>2411900</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63">
         <v>910018</v>
@@ -2732,16 +2738,16 @@
         <v>9318.43</v>
       </c>
       <c r="H63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
@@ -2752,10 +2758,10 @@
         <v>2171100</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E64">
         <v>329782.25</v>
@@ -2767,16 +2773,16 @@
         <v>29276.91</v>
       </c>
       <c r="H64" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
@@ -2787,10 +2793,10 @@
         <v>2482200</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E65">
         <v>1379406.38</v>
@@ -2802,16 +2808,16 @@
         <v>106859.4</v>
       </c>
       <c r="H65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J65" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
@@ -2822,10 +2828,10 @@
         <v>2672100</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <v>1348153.99</v>
@@ -2837,16 +2843,16 @@
         <v>88679.53</v>
       </c>
       <c r="H66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -2857,10 +2863,10 @@
         <v>545100</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E67">
         <v>252287.41</v>
@@ -2872,16 +2878,16 @@
         <v>8955</v>
       </c>
       <c r="H67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
@@ -2892,10 +2898,10 @@
         <v>534500</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E68">
         <v>291533.65000000002</v>
@@ -2907,16 +2913,16 @@
         <v>7212.06</v>
       </c>
       <c r="H68" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
@@ -2927,10 +2933,10 @@
         <v>418300</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E69">
         <v>199040.07</v>
@@ -2942,16 +2948,16 @@
         <v>17117.57</v>
       </c>
       <c r="H69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I69" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
@@ -2962,10 +2968,10 @@
         <v>540900</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E70">
         <v>224222.15</v>
@@ -2977,16 +2983,16 @@
         <v>15588.19</v>
       </c>
       <c r="H70" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
@@ -2997,10 +3003,10 @@
         <v>451900</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E71">
         <v>221495.3</v>
@@ -3012,16 +3018,16 @@
         <v>17323.61</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J71" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" t="s">
         <v>44</v>
-      </c>
-      <c r="K71" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.35">
@@ -3032,10 +3038,10 @@
         <v>2326500</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E72">
         <v>1268657.81</v>
@@ -3047,16 +3053,16 @@
         <v>105364.28</v>
       </c>
       <c r="H72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.35">
@@ -3067,10 +3073,10 @@
         <v>2156700</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E73">
         <v>1040835.91</v>
@@ -3082,16 +3088,16 @@
         <v>52360.17</v>
       </c>
       <c r="H73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I73" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.35">
@@ -3102,10 +3108,10 @@
         <v>2888200</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E74">
         <v>1699426.81</v>
@@ -3117,16 +3123,16 @@
         <v>57426.28</v>
       </c>
       <c r="H74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.35">
@@ -3137,10 +3143,10 @@
         <v>3000000</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E75">
         <v>1755790.64</v>
@@ -3152,16 +3158,16 @@
         <v>30855.1</v>
       </c>
       <c r="H75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.35">
@@ -3172,10 +3178,10 @@
         <v>2636400</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E76">
         <v>1464249.51</v>
@@ -3187,16 +3193,16 @@
         <v>12185.65</v>
       </c>
       <c r="H76" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J76" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.35">
@@ -3207,10 +3213,10 @@
         <v>1186400</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E77">
         <v>666357.93000000005</v>
@@ -3222,16 +3228,16 @@
         <v>39510.239999999998</v>
       </c>
       <c r="H77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.35">
@@ -3242,10 +3248,10 @@
         <v>1194500</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E78">
         <v>628812.38</v>
@@ -3257,16 +3263,16 @@
         <v>47778.37</v>
       </c>
       <c r="H78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.35">
@@ -3277,10 +3283,10 @@
         <v>1470900</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E79">
         <v>469484.06</v>
@@ -3292,16 +3298,16 @@
         <v>6618.49</v>
       </c>
       <c r="H79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J79" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K79" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.35">
@@ -3312,10 +3318,10 @@
         <v>1298100</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E80">
         <v>318273.34999999998</v>
@@ -3327,16 +3333,16 @@
         <v>7048.74</v>
       </c>
       <c r="H80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
@@ -3347,10 +3353,10 @@
         <v>1192700</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E81">
         <v>715056.78</v>
@@ -3362,16 +3368,16 @@
         <v>12633.71</v>
       </c>
       <c r="H81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J81" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
@@ -3382,10 +3388,10 @@
         <v>2269200</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E82">
         <v>518806.09</v>
@@ -3397,16 +3403,16 @@
         <v>40460.32</v>
       </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
@@ -3417,10 +3423,10 @@
         <v>2641800</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83">
         <v>1543262.2</v>
@@ -3432,16 +3438,16 @@
         <v>124786.03</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
@@ -3452,10 +3458,10 @@
         <v>3109800</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84">
         <v>1607999.87</v>
@@ -3467,16 +3473,16 @@
         <v>121261.24</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K84" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
@@ -3487,10 +3493,10 @@
         <v>2032800</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E85">
         <v>1019476.49</v>
@@ -3502,16 +3508,16 @@
         <v>53891.839999999997</v>
       </c>
       <c r="H85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
@@ -3522,10 +3528,10 @@
         <v>2921900</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E86">
         <v>1250023.67</v>
@@ -3537,16 +3543,16 @@
         <v>96871.48</v>
       </c>
       <c r="H86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J86" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" t="s">
         <v>44</v>
-      </c>
-      <c r="K86" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
@@ -3557,10 +3563,10 @@
         <v>1061300</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87">
         <v>246827.25</v>
@@ -3572,16 +3578,16 @@
         <v>12524.35</v>
       </c>
       <c r="H87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I87" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
@@ -3592,10 +3598,10 @@
         <v>1479100</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E88">
         <v>862499.72</v>
@@ -3607,16 +3613,16 @@
         <v>76241.42</v>
       </c>
       <c r="H88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
@@ -3627,10 +3633,10 @@
         <v>1434400</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E89">
         <v>439660.23</v>
@@ -3642,16 +3648,16 @@
         <v>13002.62</v>
       </c>
       <c r="H89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
@@ -3662,10 +3668,10 @@
         <v>1124600</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90">
         <v>555176.53</v>
@@ -3677,16 +3683,16 @@
         <v>42582.1</v>
       </c>
       <c r="H90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
@@ -3697,10 +3703,10 @@
         <v>1127100</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91">
         <v>232441.96</v>
@@ -3712,16 +3718,16 @@
         <v>14103.33</v>
       </c>
       <c r="H91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J91" t="s">
+        <v>43</v>
+      </c>
+      <c r="K91" t="s">
         <v>44</v>
-      </c>
-      <c r="K91" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.35">
@@ -3729,10 +3735,10 @@
         <v>1492100</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E92">
         <v>846995.14</v>
@@ -3744,16 +3750,16 @@
         <v>69290.37</v>
       </c>
       <c r="H92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.35">
@@ -3761,10 +3767,10 @@
         <v>1511500</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E93">
         <v>816037.51</v>
@@ -3776,16 +3782,16 @@
         <v>3040.74</v>
       </c>
       <c r="H93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K93" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.35">
@@ -3793,10 +3799,10 @@
         <v>1050900</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E94">
         <v>552148.67000000004</v>
@@ -3808,16 +3814,16 @@
         <v>4880.8100000000004</v>
       </c>
       <c r="H94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K94" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
@@ -3825,10 +3831,10 @@
         <v>1331700</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E95">
         <v>333131.42</v>
@@ -3840,16 +3846,16 @@
         <v>6240.7</v>
       </c>
       <c r="H95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I95" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.35">
@@ -3857,10 +3863,10 @@
         <v>1520300</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E96">
         <v>740299.8</v>
@@ -3872,16 +3878,16 @@
         <v>49720.29</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J96" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K96" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
@@ -3889,10 +3895,10 @@
         <v>723600</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E97">
         <v>344396.47</v>
@@ -3904,16 +3910,16 @@
         <v>29751.54</v>
       </c>
       <c r="H97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K97" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
@@ -3921,10 +3927,10 @@
         <v>876200</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E98">
         <v>420713.91</v>
@@ -3936,16 +3942,16 @@
         <v>36558.61</v>
       </c>
       <c r="H98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I98" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
@@ -3953,10 +3959,10 @@
         <v>818500</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E99">
         <v>374250.73</v>
@@ -3968,16 +3974,16 @@
         <v>12460.27</v>
       </c>
       <c r="H99" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K99" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
@@ -3985,10 +3991,10 @@
         <v>783900</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E100">
         <v>375943.58</v>
@@ -4000,16 +4006,16 @@
         <v>27081.32</v>
       </c>
       <c r="H100" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I100" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J100" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K100" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
@@ -4017,10 +4023,10 @@
         <v>699100</v>
       </c>
       <c r="C101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D101" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E101">
         <v>349000.93</v>
@@ -4032,16 +4038,16 @@
         <v>6272.16</v>
       </c>
       <c r="H101" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I101" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J101" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K101" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
@@ -4052,10 +4058,10 @@
         <v>2073300</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E102">
         <v>647323.06000000006</v>
@@ -4067,16 +4073,16 @@
         <v>52633.919999999998</v>
       </c>
       <c r="H102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K102" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
@@ -4087,10 +4093,10 @@
         <v>2101400</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E103">
         <v>1162848.3400000001</v>
@@ -4102,16 +4108,16 @@
         <v>74127.3</v>
       </c>
       <c r="H103" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K103" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
@@ -4122,10 +4128,10 @@
         <v>2463500</v>
       </c>
       <c r="C104" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D104" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E104">
         <v>1304623.44</v>
@@ -4137,16 +4143,16 @@
         <v>74220.149999999994</v>
       </c>
       <c r="H104" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K104" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
@@ -4157,10 +4163,10 @@
         <v>1988800</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D105" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E105">
         <v>1007149.42</v>
@@ -4172,16 +4178,16 @@
         <v>83572.509999999995</v>
       </c>
       <c r="H105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K105" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
@@ -4192,10 +4198,10 @@
         <v>1621100</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D106" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E106">
         <v>670527.81999999995</v>
@@ -4207,16 +4213,16 @@
         <v>37967.24</v>
       </c>
       <c r="H106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J106" t="s">
+        <v>43</v>
+      </c>
+      <c r="K106" t="s">
         <v>44</v>
-      </c>
-      <c r="K106" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
@@ -4227,10 +4233,10 @@
         <v>929900</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E107">
         <v>502523.5</v>
@@ -4242,16 +4248,16 @@
         <v>36596.46</v>
       </c>
       <c r="H107" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K107" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
@@ -4262,10 +4268,10 @@
         <v>843600</v>
       </c>
       <c r="C108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E108">
         <v>184490.4</v>
@@ -4277,16 +4283,16 @@
         <v>9871.91</v>
       </c>
       <c r="H108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
@@ -4297,10 +4303,10 @@
         <v>627200</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E109">
         <v>364124.92</v>
@@ -4312,16 +4318,16 @@
         <v>23482.6</v>
       </c>
       <c r="H109" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I109" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
@@ -4332,10 +4338,10 @@
         <v>620100</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E110">
         <v>294674.89</v>
@@ -4347,16 +4353,16 @@
         <v>16146.36</v>
       </c>
       <c r="H110" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I110" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J110" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
@@ -4367,10 +4373,10 @@
         <v>743600</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E111">
         <v>404619.73</v>
@@ -4382,16 +4388,16 @@
         <v>21000.18</v>
       </c>
       <c r="H111" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I111" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J111" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" t="s">
         <v>44</v>
-      </c>
-      <c r="K111" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
@@ -4402,10 +4408,10 @@
         <v>2071800</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E112">
         <v>694501.53</v>
@@ -4417,16 +4423,16 @@
         <v>55460.66</v>
       </c>
       <c r="H112" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I112" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K112" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.35">
@@ -4437,10 +4443,10 @@
         <v>2047500</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E113">
         <v>886017.09</v>
@@ -4452,16 +4458,16 @@
         <v>71837.62</v>
       </c>
       <c r="H113" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I113" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.35">
@@ -4472,10 +4478,10 @@
         <v>1724800</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E114">
         <v>837605.36</v>
@@ -4487,16 +4493,16 @@
         <v>70574.350000000006</v>
       </c>
       <c r="H114" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I114" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.35">
@@ -4507,10 +4513,10 @@
         <v>1817700</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D115" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E115">
         <v>1075281.8600000001</v>
@@ -4522,16 +4528,16 @@
         <v>79999.740000000005</v>
       </c>
       <c r="H115" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I115" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J115" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.35">
@@ -4542,10 +4548,10 @@
         <v>1997700</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E116">
         <v>1138443.8500000001</v>
@@ -4557,16 +4563,16 @@
         <v>33022.49</v>
       </c>
       <c r="H116" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I116" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J116" t="s">
+        <v>43</v>
+      </c>
+      <c r="K116" t="s">
         <v>44</v>
-      </c>
-      <c r="K116" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.35">
@@ -4577,10 +4583,10 @@
         <v>1844500</v>
       </c>
       <c r="C117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E117">
         <v>1030132.66</v>
@@ -4592,16 +4598,16 @@
         <v>52133.02</v>
       </c>
       <c r="H117" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I117" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K117" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.35">
@@ -4612,10 +4618,10 @@
         <v>1249000</v>
       </c>
       <c r="C118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E118">
         <v>728930.71</v>
@@ -4627,16 +4633,16 @@
         <v>50829.01</v>
       </c>
       <c r="H118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I118" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J118" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K118" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.35">
@@ -4647,10 +4653,10 @@
         <v>1447200</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E119">
         <v>825013.97</v>
@@ -4662,16 +4668,16 @@
         <v>19717.96</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J119" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K119" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.35">
@@ -4682,10 +4688,10 @@
         <v>1711800</v>
       </c>
       <c r="C120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E120">
         <v>754942.8</v>
@@ -4697,16 +4703,16 @@
         <v>46322.38</v>
       </c>
       <c r="H120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I120" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J120" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.35">
@@ -4717,10 +4723,10 @@
         <v>1315500</v>
       </c>
       <c r="C121" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E121">
         <v>549311.36</v>
@@ -4732,16 +4738,16 @@
         <v>36198.720000000001</v>
       </c>
       <c r="H121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J121" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K121" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.35">
@@ -4752,10 +4758,10 @@
         <v>898000</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E122">
         <v>472151.34</v>
@@ -4767,16 +4773,16 @@
         <v>24289.32</v>
       </c>
       <c r="H122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I122" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K122" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.35">
@@ -4787,10 +4793,10 @@
         <v>1168400</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E123">
         <v>473560.56</v>
@@ -4802,16 +4808,16 @@
         <v>41352.879999999997</v>
       </c>
       <c r="H123" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I123" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J123" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K123" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.35">
@@ -4822,10 +4828,10 @@
         <v>961200</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E124">
         <v>409253.98</v>
@@ -4837,16 +4843,16 @@
         <v>27266.78</v>
       </c>
       <c r="H124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I124" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J124" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K124" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.35">
@@ -4857,10 +4863,10 @@
         <v>1234200</v>
       </c>
       <c r="C125" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E125">
         <v>237312.45</v>
@@ -4872,16 +4878,16 @@
         <v>21296.84</v>
       </c>
       <c r="H125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I125" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J125" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.35">
@@ -4892,10 +4898,10 @@
         <v>1144400</v>
       </c>
       <c r="C126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D126" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E126">
         <v>272985.93</v>
@@ -4907,16 +4913,16 @@
         <v>20769.099999999999</v>
       </c>
       <c r="H126" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J126" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.35">
@@ -4927,10 +4933,10 @@
         <v>1311700</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D127" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E127">
         <v>614910.42000000004</v>
@@ -4942,16 +4948,16 @@
         <v>19709.439999999999</v>
       </c>
       <c r="H127" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K127" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.35">
@@ -4962,10 +4968,10 @@
         <v>1622900</v>
       </c>
       <c r="C128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D128" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E128">
         <v>949572.21</v>
@@ -4977,16 +4983,16 @@
         <v>36044.46</v>
       </c>
       <c r="H128" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I128" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K128" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.35">
@@ -4997,10 +5003,10 @@
         <v>1731100</v>
       </c>
       <c r="C129" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E129">
         <v>977485.99</v>
@@ -5012,16 +5018,16 @@
         <v>30206.67</v>
       </c>
       <c r="H129" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I129" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.35">
@@ -5032,10 +5038,10 @@
         <v>1564300</v>
       </c>
       <c r="C130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E130">
         <v>561095.97</v>
@@ -5047,16 +5053,16 @@
         <v>32646.89</v>
       </c>
       <c r="H130" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J130" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.35">
@@ -5067,10 +5073,10 @@
         <v>1226700</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D131" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E131">
         <v>613437.55000000005</v>
@@ -5082,16 +5088,16 @@
         <v>26627.32</v>
       </c>
       <c r="H131" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I131" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J131" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K131" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.35">
@@ -5102,10 +5108,10 @@
         <v>1893700</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E132">
         <v>490738.77</v>
@@ -5117,16 +5123,16 @@
         <v>34736.300000000003</v>
       </c>
       <c r="H132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K132" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.35">
@@ -5137,10 +5143,10 @@
         <v>2492100</v>
       </c>
       <c r="C133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E133">
         <v>727989.41</v>
@@ -5152,16 +5158,16 @@
         <v>33906.61</v>
       </c>
       <c r="H133" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I133" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K133" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.35">
@@ -5172,10 +5178,10 @@
         <v>2462300</v>
       </c>
       <c r="C134" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D134" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E134">
         <v>1229831.3</v>
@@ -5187,16 +5193,16 @@
         <v>79348.52</v>
       </c>
       <c r="H134" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I134" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K134" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.35">
@@ -5207,10 +5213,10 @@
         <v>1862900</v>
       </c>
       <c r="C135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E135">
         <v>915252.78</v>
@@ -5222,16 +5228,16 @@
         <v>13594.72</v>
       </c>
       <c r="H135" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I135" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J135" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K135" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.35">
@@ -5242,10 +5248,10 @@
         <v>2000900</v>
       </c>
       <c r="C136" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D136" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E136">
         <v>881079.38</v>
@@ -5257,16 +5263,16 @@
         <v>47096.02</v>
       </c>
       <c r="H136" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I136" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J136" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K136" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.35">
@@ -5277,10 +5283,10 @@
         <v>1057400</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E137">
         <v>250925.18</v>
@@ -5292,16 +5298,16 @@
         <v>15523.41</v>
       </c>
       <c r="H137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I137" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K137" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.35">
@@ -5312,10 +5318,10 @@
         <v>1228400</v>
       </c>
       <c r="C138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E138">
         <v>600349.27</v>
@@ -5327,16 +5333,16 @@
         <v>26891.98</v>
       </c>
       <c r="H138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I138" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.35">
@@ -5347,10 +5353,10 @@
         <v>1088900</v>
       </c>
       <c r="C139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D139" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E139">
         <v>405377.09</v>
@@ -5362,16 +5368,16 @@
         <v>21746.400000000001</v>
       </c>
       <c r="H139" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I139" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K139" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.35">
@@ -5382,10 +5388,10 @@
         <v>992600</v>
       </c>
       <c r="C140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D140" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E140">
         <v>403421.16</v>
@@ -5397,16 +5403,16 @@
         <v>8414.18</v>
       </c>
       <c r="H140" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I140" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J140" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.35">
@@ -5417,10 +5423,10 @@
         <v>1024900</v>
       </c>
       <c r="C141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D141" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E141">
         <v>157394.93</v>
@@ -5432,16 +5438,16 @@
         <v>8044.73</v>
       </c>
       <c r="H141" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I141" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J141" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K141" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.35">
@@ -5452,10 +5458,10 @@
         <v>1180400</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E142">
         <v>667762.38</v>
@@ -5467,16 +5473,16 @@
         <v>47265.35</v>
       </c>
       <c r="H142" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I142" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J142" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K142" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.35">
@@ -5487,10 +5493,10 @@
         <v>1246400</v>
       </c>
       <c r="C143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D143" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E143">
         <v>651751.9</v>
@@ -5502,16 +5508,16 @@
         <v>43048.03</v>
       </c>
       <c r="H143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K143" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.35">
@@ -5522,10 +5528,10 @@
         <v>1445600</v>
       </c>
       <c r="C144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E144">
         <v>233045.4</v>
@@ -5537,16 +5543,16 @@
         <v>16766.97</v>
       </c>
       <c r="H144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I144" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K144" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.35">
@@ -5557,10 +5563,10 @@
         <v>1359700</v>
       </c>
       <c r="C145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E145">
         <v>612966.77</v>
@@ -5572,16 +5578,16 @@
         <v>9141.1</v>
       </c>
       <c r="H145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I145" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J145" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.35">
@@ -5592,10 +5598,10 @@
         <v>1205600</v>
       </c>
       <c r="C146" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D146" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E146">
         <v>607849.54</v>
@@ -5607,16 +5613,16 @@
         <v>45010.44</v>
       </c>
       <c r="H146" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I146" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J146" t="s">
+        <v>43</v>
+      </c>
+      <c r="K146" t="s">
         <v>44</v>
-      </c>
-      <c r="K146" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.35">
@@ -5627,10 +5633,10 @@
         <v>692100</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D147" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E147">
         <v>343770.09</v>
@@ -5642,16 +5648,16 @@
         <v>27577.43</v>
       </c>
       <c r="H147" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I147" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J147" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K147" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
@@ -5662,10 +5668,10 @@
         <v>679300</v>
       </c>
       <c r="C148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D148" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E148">
         <v>347581.79</v>
@@ -5677,16 +5683,16 @@
         <v>19322.29</v>
       </c>
       <c r="H148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I148" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J148" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K148" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.35">
@@ -5697,10 +5703,10 @@
         <v>702600</v>
       </c>
       <c r="C149" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E149">
         <v>300753.78000000003</v>
@@ -5712,16 +5718,16 @@
         <v>16905.509999999998</v>
       </c>
       <c r="H149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I149" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K149" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
@@ -5732,10 +5738,10 @@
         <v>900100</v>
       </c>
       <c r="C150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D150" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E150">
         <v>450054.09</v>
@@ -5747,16 +5753,16 @@
         <v>37367.730000000003</v>
       </c>
       <c r="H150" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J150" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K150" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.35">
@@ -5767,10 +5773,10 @@
         <v>670900</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D151" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E151">
         <v>254068.96</v>
@@ -5782,16 +5788,16 @@
         <v>7877.87</v>
       </c>
       <c r="H151" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I151" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J151" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K151" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.35">
@@ -5802,10 +5808,10 @@
         <v>106700</v>
       </c>
       <c r="C152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E152">
         <v>55896.37</v>
@@ -5817,16 +5823,16 @@
         <v>1949.15</v>
       </c>
       <c r="I152" t="s">
+        <v>38</v>
+      </c>
+      <c r="J152" t="s">
         <v>39</v>
       </c>
-      <c r="J152" t="s">
-        <v>40</v>
-      </c>
       <c r="K152" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L152" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.35">
@@ -5837,10 +5843,10 @@
         <v>117200</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E153">
         <v>32004.400000000001</v>
@@ -5852,16 +5858,16 @@
         <v>1284.56</v>
       </c>
       <c r="I153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K153" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L153" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.35">
@@ -5872,10 +5878,10 @@
         <v>81300</v>
       </c>
       <c r="C154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E154">
         <v>21452.82</v>
@@ -5887,16 +5893,16 @@
         <v>1570.27</v>
       </c>
       <c r="I154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K154" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L154" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.35">
@@ -5907,10 +5913,10 @@
         <v>119200</v>
       </c>
       <c r="C155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E155">
         <v>70257.3</v>
@@ -5922,16 +5928,16 @@
         <v>5464.43</v>
       </c>
       <c r="I155" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J155" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K155" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L155" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.35">
@@ -5942,10 +5948,10 @@
         <v>118000</v>
       </c>
       <c r="C156" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="D156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E156">
         <v>56772.2</v>
@@ -5957,16 +5963,16 @@
         <v>4364</v>
       </c>
       <c r="I156" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J156" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K156" t="s">
+        <v>46</v>
+      </c>
+      <c r="L156" t="s">
         <v>47</v>
-      </c>
-      <c r="L156" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
